--- a/config/excel/CfgProfile.xlsx
+++ b/config/excel/CfgProfile.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgProfile" sheetId="1" r:id="R0cdc0dfae2e14a2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgProfile" sheetId="1" r:id="R6973879c5363477c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -486,6 +486,9 @@
       <x:c r="AJ1" s="9" t="str">
         <x:v>StarterQuality</x:v>
       </x:c>
+      <x:c r="AK1" t="str">
+        <x:v>RunHistoryLimit</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="10" t="str">
@@ -594,6 +597,9 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="AJ2" s="10" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AK2" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
@@ -706,6 +712,9 @@
       <x:c r="AJ3" s="12" t="str">
         <x:v>初始物品品质枚举值</x:v>
       </x:c>
+      <x:c r="AK3" t="str">
+        <x:v># 战绩历史上限</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="6" t="n">
@@ -815,6 +824,9 @@
       </x:c>
       <x:c r="AJ4" s="6" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK4" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgProfile.xlsx
+++ b/config/excel/CfgProfile.xlsx
@@ -784,7 +784,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="W4" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="X4" s="6" t="n">
         <x:v>10</x:v>

--- a/config/excel/CfgProfile.xlsx
+++ b/config/excel/CfgProfile.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgProfile" sheetId="1" r:id="R6973879c5363477c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgProfile" sheetId="1" r:id="R7e511ef5dcb74f45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -781,7 +781,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="V4" s="6" t="n">
-        <x:v>1.5</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="W4" s="6" t="n">
         <x:v>6.5</x:v>

--- a/config/excel/CfgProfile.xlsx
+++ b/config/excel/CfgProfile.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgProfile" sheetId="1" r:id="R7e511ef5dcb74f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgProfile" sheetId="1" r:id="Rea506f3b8a9d414a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,34 +346,34 @@
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="19.799999237060547" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20.899999618530273" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="17.600000381469727" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="20.899999618530273" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="19.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="19.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="17.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="19.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="16" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="18.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="18.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="16" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="16" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="16" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="29" max="29" width="16" hidden="0" customWidth="1"/>
-    <x:col min="30" max="30" width="20.899999618530273" hidden="0" customWidth="1"/>
-    <x:col min="31" max="31" width="18.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="19.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="16" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="20.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="18.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="16.5" hidden="0" customWidth="1"/>
     <x:col min="32" max="32" width="16.5" hidden="0" customWidth="1"/>
-    <x:col min="33" max="33" width="16.5" hidden="0" customWidth="1"/>
-    <x:col min="34" max="34" width="17.600000381469727" hidden="0" customWidth="1"/>
-    <x:col min="35" max="35" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="17.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="16" hidden="0" customWidth="1"/>
     <x:col min="36" max="36" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -400,95 +400,93 @@
         <x:v>DailyResetHour</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>SafeSlots</x:v>
+        <x:v>SkillPointsPerLevel</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
-        <x:v>SkillPointsPerLevel</x:v>
+        <x:v>ExtractionExperience</x:v>
       </x:c>
       <x:c r="J1" s="9" t="str">
-        <x:v>ExtractionExperience</x:v>
+        <x:v>KeepKillExperienceOnDeath</x:v>
       </x:c>
       <x:c r="K1" s="9" t="str">
-        <x:v>KeepKillExperienceOnDeath</x:v>
+        <x:v>NpcItemPrice</x:v>
       </x:c>
       <x:c r="L1" s="9" t="str">
-        <x:v>NpcItemPrice</x:v>
+        <x:v>ExperienceBase</x:v>
       </x:c>
       <x:c r="M1" s="9" t="str">
-        <x:v>ExperienceBase</x:v>
+        <x:v>ExperiencePerLevel</x:v>
       </x:c>
       <x:c r="N1" s="9" t="str">
-        <x:v>ExperiencePerLevel</x:v>
+        <x:v>StartingLevel</x:v>
       </x:c>
       <x:c r="O1" s="9" t="str">
-        <x:v>StartingLevel</x:v>
+        <x:v>StartingExperience</x:v>
       </x:c>
       <x:c r="P1" s="9" t="str">
-        <x:v>StartingExperience</x:v>
+        <x:v>StartingGold</x:v>
       </x:c>
       <x:c r="Q1" s="9" t="str">
-        <x:v>StartingGold</x:v>
+        <x:v>StartingDiamonds</x:v>
       </x:c>
       <x:c r="R1" s="9" t="str">
-        <x:v>StartingDiamonds</x:v>
+        <x:v>StartingSkillPoints</x:v>
       </x:c>
       <x:c r="S1" s="9" t="str">
-        <x:v>StartingSkillPoints</x:v>
+        <x:v>BaseMaxHealth</x:v>
       </x:c>
       <x:c r="T1" s="9" t="str">
-        <x:v>BaseMaxHealth</x:v>
+        <x:v>BaseCriticalDamage</x:v>
       </x:c>
       <x:c r="U1" s="9" t="str">
-        <x:v>BaseCriticalDamage</x:v>
+        <x:v>BaseAttackRange</x:v>
       </x:c>
       <x:c r="V1" s="9" t="str">
-        <x:v>BaseAttackRange</x:v>
+        <x:v>BaseMoveSpeed</x:v>
       </x:c>
       <x:c r="W1" s="9" t="str">
-        <x:v>BaseMoveSpeed</x:v>
+        <x:v>UnarmedAttack</x:v>
       </x:c>
       <x:c r="X1" s="9" t="str">
-        <x:v>UnarmedAttack</x:v>
+        <x:v>MaxAttributeValue</x:v>
       </x:c>
       <x:c r="Y1" s="9" t="str">
-        <x:v>MaxAttributeValue</x:v>
+        <x:v>MaxAttackRange</x:v>
       </x:c>
       <x:c r="Z1" s="9" t="str">
-        <x:v>MaxAttackRange</x:v>
+        <x:v>MaxDodgeChance</x:v>
       </x:c>
       <x:c r="AA1" s="9" t="str">
-        <x:v>MaxDodgeChance</x:v>
+        <x:v>MaxDamageReduction</x:v>
       </x:c>
       <x:c r="AB1" s="9" t="str">
-        <x:v>MaxDamageReduction</x:v>
+        <x:v>MaxLevel</x:v>
       </x:c>
       <x:c r="AC1" s="9" t="str">
-        <x:v>MaxLevel</x:v>
+        <x:v>StarterDefinitionId</x:v>
       </x:c>
       <x:c r="AD1" s="9" t="str">
-        <x:v>StarterDefinitionId</x:v>
+        <x:v>DefaultLootPoolID</x:v>
       </x:c>
       <x:c r="AE1" s="9" t="str">
-        <x:v>DefaultLootPoolID</x:v>
+        <x:v>AffixLevelScale</x:v>
       </x:c>
       <x:c r="AF1" s="9" t="str">
-        <x:v>AffixLevelScale</x:v>
+        <x:v>SupplyHourFirst</x:v>
       </x:c>
       <x:c r="AG1" s="9" t="str">
-        <x:v>SupplyHourFirst</x:v>
+        <x:v>SupplyHourSecond</x:v>
       </x:c>
       <x:c r="AH1" s="9" t="str">
-        <x:v>SupplyHourSecond</x:v>
+        <x:v>SupplyHourThird</x:v>
       </x:c>
       <x:c r="AI1" s="9" t="str">
-        <x:v>SupplyHourThird</x:v>
+        <x:v>StarterQuality</x:v>
       </x:c>
       <x:c r="AJ1" s="9" t="str">
-        <x:v>StarterQuality</x:v>
-      </x:c>
-      <x:c r="AK1" t="str">
         <x:v>RunHistoryLimit</x:v>
       </x:c>
+      <x:c r="AK1"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="10" t="str">
@@ -519,10 +517,10 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>int</x:v>
+        <x:v>bool</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>bool</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
         <x:v>int</x:v>
@@ -546,7 +544,7 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="S2" s="10" t="str">
-        <x:v>int</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="T2" s="10" t="str">
         <x:v>number</x:v>
@@ -573,19 +571,19 @@
         <x:v>number</x:v>
       </x:c>
       <x:c r="AB2" s="10" t="str">
-        <x:v>number</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="AC2" s="10" t="str">
-        <x:v>int</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="AD2" s="10" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="AE2" s="10" t="str">
-        <x:v>string</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="AF2" s="10" t="str">
-        <x:v>number</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="AG2" s="10" t="str">
         <x:v>int</x:v>
@@ -599,9 +597,7 @@
       <x:c r="AJ2" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="AK2" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="AK2"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="12" t="str">
@@ -626,95 +622,93 @@
         <x:v>每日体力重置小时</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>安全箱容量</x:v>
+        <x:v>每级技能点</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
-        <x:v>每级技能点</x:v>
+        <x:v>成功撤离经验</x:v>
       </x:c>
       <x:c r="J3" s="12" t="str">
-        <x:v>成功撤离经验</x:v>
+        <x:v>死亡保留击杀经验</x:v>
       </x:c>
       <x:c r="K3" s="12" t="str">
-        <x:v>死亡保留击杀经验</x:v>
+        <x:v>商店测试物品价格</x:v>
       </x:c>
       <x:c r="L3" s="12" t="str">
-        <x:v>商店测试物品价格</x:v>
+        <x:v>一级升级经验</x:v>
       </x:c>
       <x:c r="M3" s="12" t="str">
-        <x:v>一级升级经验</x:v>
+        <x:v>每级经验增量</x:v>
       </x:c>
       <x:c r="N3" s="12" t="str">
-        <x:v>每级经验增量</x:v>
+        <x:v>新档等级</x:v>
       </x:c>
       <x:c r="O3" s="12" t="str">
-        <x:v>新档等级</x:v>
+        <x:v>新档经验</x:v>
       </x:c>
       <x:c r="P3" s="12" t="str">
-        <x:v>新档经验</x:v>
+        <x:v>新档金币</x:v>
       </x:c>
       <x:c r="Q3" s="12" t="str">
-        <x:v>新档金币</x:v>
+        <x:v>新档钻石</x:v>
       </x:c>
       <x:c r="R3" s="12" t="str">
-        <x:v>新档钻石</x:v>
+        <x:v>新档技能点</x:v>
       </x:c>
       <x:c r="S3" s="12" t="str">
-        <x:v>新档技能点</x:v>
+        <x:v>基础生命</x:v>
       </x:c>
       <x:c r="T3" s="12" t="str">
-        <x:v>基础生命</x:v>
+        <x:v>基础暴击伤害倍率</x:v>
       </x:c>
       <x:c r="U3" s="12" t="str">
-        <x:v>基础暴击伤害倍率</x:v>
+        <x:v>基础攻击射程</x:v>
       </x:c>
       <x:c r="V3" s="12" t="str">
-        <x:v>基础攻击射程</x:v>
+        <x:v>基础移速</x:v>
       </x:c>
       <x:c r="W3" s="12" t="str">
-        <x:v>基础移速</x:v>
+        <x:v>无武器攻击</x:v>
       </x:c>
       <x:c r="X3" s="12" t="str">
-        <x:v>无武器攻击</x:v>
+        <x:v>属性最大校验值</x:v>
       </x:c>
       <x:c r="Y3" s="12" t="str">
-        <x:v>属性最大校验值</x:v>
+        <x:v>攻击射程最大校验值</x:v>
       </x:c>
       <x:c r="Z3" s="12" t="str">
-        <x:v>攻击射程最大校验值</x:v>
+        <x:v>闪避上限</x:v>
       </x:c>
       <x:c r="AA3" s="12" t="str">
-        <x:v>闪避上限</x:v>
+        <x:v>减伤上限</x:v>
       </x:c>
       <x:c r="AB3" s="12" t="str">
-        <x:v>减伤上限</x:v>
+        <x:v>等级上限</x:v>
       </x:c>
       <x:c r="AC3" s="12" t="str">
-        <x:v>等级上限</x:v>
+        <x:v>新档初始物品定义</x:v>
       </x:c>
       <x:c r="AD3" s="12" t="str">
-        <x:v>新档初始物品定义</x:v>
+        <x:v>默认掉落池身份</x:v>
       </x:c>
       <x:c r="AE3" s="12" t="str">
-        <x:v>默认掉落池身份</x:v>
+        <x:v>词条每级成长比例</x:v>
       </x:c>
       <x:c r="AF3" s="12" t="str">
-        <x:v>词条每级成长比例</x:v>
+        <x:v>首个补给时段开始小时</x:v>
       </x:c>
       <x:c r="AG3" s="12" t="str">
-        <x:v>首个补给时段开始小时</x:v>
+        <x:v>第二补给时段开始小时</x:v>
       </x:c>
       <x:c r="AH3" s="12" t="str">
-        <x:v>第二补给时段开始小时</x:v>
+        <x:v>第三补给时段开始小时</x:v>
       </x:c>
       <x:c r="AI3" s="12" t="str">
-        <x:v>第三补给时段开始小时</x:v>
+        <x:v>初始物品品质枚举值</x:v>
       </x:c>
       <x:c r="AJ3" s="12" t="str">
-        <x:v>初始物品品质枚举值</x:v>
-      </x:c>
-      <x:c r="AK3" t="str">
         <x:v># 战绩历史上限</x:v>
       </x:c>
+      <x:c r="AK3"/>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="6" t="n">
@@ -739,95 +733,93 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H4" s="6" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="6" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="6" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="b">
+      <x:c r="K4" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="M4" s="6" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N4" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L4" s="6" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="M4" s="6" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="N4" s="6" t="n">
+      <x:c r="O4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="6" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="O4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P4" s="6" t="n">
+      <x:c r="Q4" s="6" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q4" s="6" t="n">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="R4" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="S4" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="T4" s="6" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U4" s="6" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="V4" s="6" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="W4" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="X4" s="6" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="Y4" s="6" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="U4" s="6" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="V4" s="6" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="W4" s="6" t="n">
-        <x:v>6.5</x:v>
-      </x:c>
-      <x:c r="X4" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Y4" s="6" t="n">
-        <x:v>1000000</x:v>
-      </x:c>
       <x:c r="Z4" s="6" t="n">
-        <x:v>100</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="AA4" s="6" t="n">
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="AB4" s="6" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="AC4" s="6" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="AC4" s="6" t="str">
+        <x:v>starter_weapon</x:v>
+      </x:c>
       <x:c r="AD4" s="13" t="str">
-        <x:v>starter_weapon</x:v>
-      </x:c>
-      <x:c r="AE4" s="13" t="str">
         <x:v>default</x:v>
       </x:c>
+      <x:c r="AE4" s="13" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
       <x:c r="AF4" s="6" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AG4" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AH4" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="AI4" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AH4" s="6" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="AI4" s="6" t="n">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="AJ4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AK4" t="n">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="AK4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
